--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T10:56:37+00:00</t>
+    <t>2025-01-17T11:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -10,12 +10,15 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T11:40:58+00:00</t>
+    <t>2025-01-21T12:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,13 +120,22 @@
     <t>System URI</t>
   </si>
   <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/icd-10-bmsgpk-2025</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/icpc2</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/icf</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/lkat-bmsgpk-2025</t>
+  </si>
+  <si>
     <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/sid/icd-10-cm</t>
   </si>
 </sst>
 </file>
@@ -505,4 +517,124 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -59,13 +59,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-21T12:24:15+00:00</t>
+    <t>2025-01-23T11:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:46:49+00:00</t>
+    <t>2025-01-24T11:26:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T11:26:43+00:00</t>
+    <t>2025-01-29T08:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T08:49:29+00:00</t>
+    <t>2025-01-29T12:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-condition-code-systems.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T12:34:29+00:00</t>
+    <t>2025-02-03T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
